--- a/downloads/purchasing/dixani-supplier-comparison-sheet.xlsx
+++ b/downloads/purchasing/dixani-supplier-comparison-sheet.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Comparison" sheetId="1" r:id="R629205fc1e824a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="2" r:id="Re02575aa8be541cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="3" r:id="Ra89e3c85553f4e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Comparison" sheetId="1" r:id="Rafdc25dcaae84856"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example" sheetId="2" r:id="Rb56ab11ff8f743bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="3" r:id="R8308c389429a4e3e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -253,7 +253,7 @@
         <x:color rgb="FF15803D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -264,7 +264,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -557,7 +557,9 @@
       <x:c r="I4" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="J4"/>
+      <x:c r="J4" t="str">
+        <x:v>USD</x:v>
+      </x:c>
       <x:c r="K4" t="str">
         <x:v>Evaluation Date</x:v>
       </x:c>
@@ -1709,7 +1711,7 @@
   </x:conditionalFormatting>
   <x:dataValidations count="9">
     <x:dataValidation type="list" sqref="J4">
-      <x:formula1>"QAR,USD,EUR,GBP,AED,SAR,LKR,INR"</x:formula1>
+      <x:formula1>"USD,EUR,GBP,CAD,AUD,NZD,CHF,JPY,CNY,HKD,SGD,INR,AED,SAR,QAR,LKR,ZAR,BRL,MXN"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="C17:G18">
       <x:formula1>"1,2,3,4,5"</x:formula1>
